--- a/downloads/en/acces-ouvert-rattachement.xlsx
+++ b/downloads/en/acces-ouvert-rattachement.xlsx
@@ -466,7 +466,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
@@ -488,7 +488,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C5" t="n">
         <v>47</v>
